--- a/output/pdf_financials_xlsx/RSS.xlsx
+++ b/output/pdf_financials_xlsx/RSS.xlsx
@@ -5925,52 +5925,52 @@
         <v>0.29658</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0.61158</v>
+        <v>0.29658</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>2.094336</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>2.646285</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>4.171583</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>7.862638</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>7.661465</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>11.884059</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>12.930118</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>14.497644</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>14.991524</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>15.212817</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>14.01715</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>13.930836</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>15.093903</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>15.336725</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>15.361084</v>
       </c>
     </row>
     <row r="93">
@@ -10162,7 +10162,11 @@
           <t>Share-based payment reserve (Note 7)</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
           <t>-</t>
@@ -11366,7 +11370,11 @@
           <t>Share-based payment reserve (Note 10)</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E31" t="inlineStr">
         <is>
           <t>-</t>
@@ -12346,7 +12354,11 @@
           <t>Share-based payment reserve (Note 11)</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr"/>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E41" t="inlineStr">
         <is>
           <t>-</t>
@@ -13449,7 +13461,11 @@
           <t>Share-based payment reserve (Notes 10 and 11)</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr"/>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E52" t="inlineStr">
         <is>
           <t>-</t>
@@ -14433,7 +14449,11 @@
           <t>Share-based payment reserve</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr"/>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E62" t="inlineStr">
         <is>
           <t>-</t>
@@ -17320,7 +17340,11 @@
           <t>Share-based payment reserve 2,094,336</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr"/>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E91" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/RSS.xlsx
+++ b/output/pdf_financials_xlsx/RSS.xlsx
@@ -1065,49 +1065,49 @@
         <v>0</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.013979</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.044825</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.032815</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.020131</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.01576</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.030542</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.019405</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.010388</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.006809</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.004734</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>0.00025</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>0.00246</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>0.00165</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>0.001731</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>0</v>
+        <v>0.000339</v>
       </c>
     </row>
     <row r="13">
@@ -2007,49 +2007,49 @@
         <v>-0.461672</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-2.616851</v>
+        <v>-2.63083</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-1.917225</v>
+        <v>-1.96205</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-5.413777</v>
+        <v>-5.446592</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-7.840441</v>
+        <v>-7.860572</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-5.011241</v>
+        <v>-5.027001</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-8.086736999999999</v>
+        <v>-8.117279</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-7.617012</v>
+        <v>-7.636417</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-5.845123</v>
+        <v>-5.855511</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-3.125533</v>
+        <v>-3.132342</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-2.780329</v>
+        <v>-2.785063</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-2.833571</v>
+        <v>-2.833821</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-1.188717</v>
+        <v>-1.191177</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-2.257203</v>
+        <v>-2.258853</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>-1.122328</v>
+        <v>-1.124059</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>-0.055655</v>
+        <v>-0.055994</v>
       </c>
     </row>
     <row r="28">
@@ -2123,49 +2123,49 @@
         <v>-0.461672</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-2.616851</v>
+        <v>-2.63083</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-1.917225</v>
+        <v>-1.96205</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-5.413777</v>
+        <v>-5.446592</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-7.840441</v>
+        <v>-7.860572</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-5.011241</v>
+        <v>-5.027001</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-8.086736999999999</v>
+        <v>-8.117279</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-7.617012</v>
+        <v>-7.636417</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-5.845123</v>
+        <v>-5.855511</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-3.125533</v>
+        <v>-3.132342</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-2.780329</v>
+        <v>-2.785063</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-2.833571</v>
+        <v>-2.833821</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-1.188717</v>
+        <v>-1.191177</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-2.257203</v>
+        <v>-2.258853</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-1.122328</v>
+        <v>-1.124059</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>-0.055655</v>
+        <v>-0.055994</v>
       </c>
     </row>
     <row r="30">
@@ -2200,40 +2200,40 @@
         </is>
       </c>
       <c r="G30" s="3" t="n">
-        <v>-116899.3737885791</v>
+        <v>-117199.5228865365</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>-4675.013993581611</v>
+        <v>-4689.716583327114</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>-2653.83418821931</v>
+        <v>-2663.857193020455</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>-1707.888517679769</v>
+        <v>-1712.239512096684</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>-945.580213280876</v>
+        <v>-947.2607061046474</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>-389.5784047085453</v>
+        <v>-390.427104548752</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>-423.3356730773623</v>
+        <v>-424.0564766500144</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>-505.9731368655629</v>
+        <v>-506.0177778095224</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>-317.4763037921945</v>
+        <v>-318.1333076941567</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>-555.5945828861737</v>
+        <v>-556.0007187373852</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>-313.4906846177481</v>
+        <v>-313.9741906650652</v>
       </c>
       <c r="R30" s="3" t="n">
-        <v>-6.303901158273169</v>
+        <v>-6.342298831306223</v>
       </c>
     </row>
     <row r="31">
@@ -2375,10 +2375,8 @@
           <t xml:space="preserve">    Cash and Cash Equivalents</t>
         </is>
       </c>
-      <c r="B34" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B34" s="3" t="n">
+        <v>0.122214</v>
       </c>
       <c r="C34" s="3" t="n">
         <v>0.122214</v>
@@ -2495,10 +2493,8 @@
           <t xml:space="preserve">  Cash, Cash Equivalents, Marketable Securities</t>
         </is>
       </c>
-      <c r="B36" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B36" s="3" t="n">
+        <v>0.122214</v>
       </c>
       <c r="C36" s="3" t="n">
         <v>0.122214</v>
@@ -17750,7 +17746,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E95" s="5" t="n">
@@ -31505,7 +31501,7 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
@@ -43076,7 +43072,7 @@
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E355" t="inlineStr">
@@ -50227,7 +50223,7 @@
       </c>
       <c r="D426" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E426" t="inlineStr">

--- a/output/pdf_financials_xlsx/RSS.xlsx
+++ b/output/pdf_financials_xlsx/RSS.xlsx
@@ -4592,19 +4592,19 @@
         <v>0</v>
       </c>
       <c r="L70" s="3" t="n">
-        <v>0</v>
+        <v>0.17728</v>
       </c>
       <c r="M70" s="3" t="n">
-        <v>0</v>
+        <v>0.044353</v>
       </c>
       <c r="N70" s="3" t="n">
-        <v>0</v>
+        <v>0.006931</v>
       </c>
       <c r="O70" s="3" t="n">
-        <v>0</v>
+        <v>0.014493</v>
       </c>
       <c r="P70" s="3" t="n">
-        <v>0</v>
+        <v>0.015541</v>
       </c>
       <c r="Q70" s="3" t="n">
         <v>0</v>
@@ -4652,19 +4652,19 @@
         <v>0</v>
       </c>
       <c r="L71" s="3" t="n">
-        <v>0</v>
+        <v>0.17728</v>
       </c>
       <c r="M71" s="3" t="n">
-        <v>0</v>
+        <v>0.044353</v>
       </c>
       <c r="N71" s="3" t="n">
-        <v>0</v>
+        <v>0.006931</v>
       </c>
       <c r="O71" s="3" t="n">
-        <v>0</v>
+        <v>0.014493</v>
       </c>
       <c r="P71" s="3" t="n">
-        <v>0</v>
+        <v>0.015541</v>
       </c>
       <c r="Q71" s="3" t="n">
         <v>0</v>
@@ -4892,19 +4892,19 @@
         <v>0.041024</v>
       </c>
       <c r="L75" s="3" t="n">
-        <v>0.17728</v>
+        <v>0</v>
       </c>
       <c r="M75" s="3" t="n">
-        <v>0.044353</v>
+        <v>0</v>
       </c>
       <c r="N75" s="3" t="n">
-        <v>0.10083</v>
+        <v>0.093899</v>
       </c>
       <c r="O75" s="3" t="n">
-        <v>0.293418</v>
+        <v>0.278925</v>
       </c>
       <c r="P75" s="3" t="n">
-        <v>0.492717</v>
+        <v>0.477176</v>
       </c>
       <c r="Q75" s="3" t="n">
         <v>0.683732</v>
@@ -5215,30 +5215,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L80" s="3" t="n">
+        <v>0.2288904468450742</v>
+      </c>
+      <c r="M80" s="3" t="n">
+        <v>-1.375670729816073</v>
+      </c>
+      <c r="N80" s="3" t="n">
+        <v>-0.0271800723913052</v>
+      </c>
+      <c r="O80" s="3" t="n">
+        <v>-0.03344872948833345</v>
+      </c>
+      <c r="P80" s="3" t="n">
+        <v>-0.3108697391582653</v>
       </c>
       <c r="Q80" s="1" t="inlineStr">
         <is>
@@ -7278,25 +7268,25 @@
         <v>0</v>
       </c>
       <c r="E116" s="3" t="n">
-        <v>0</v>
+        <v>-0.010089</v>
       </c>
       <c r="F116" s="3" t="n">
-        <v>0</v>
+        <v>-0.008699999999999999</v>
       </c>
       <c r="G116" s="3" t="n">
-        <v>0</v>
+        <v>-0.010377</v>
       </c>
       <c r="H116" s="3" t="n">
-        <v>0</v>
+        <v>-0.012638</v>
       </c>
       <c r="I116" s="3" t="n">
-        <v>0</v>
+        <v>-0.010331</v>
       </c>
       <c r="J116" s="3" t="n">
-        <v>0</v>
+        <v>-0.013852</v>
       </c>
       <c r="K116" s="3" t="n">
-        <v>0</v>
+        <v>-0.001181</v>
       </c>
       <c r="L116" s="3" t="n">
         <v>0</v>
@@ -12150,7 +12140,11 @@
           <t>Lease liabilities (Note 7 and 14(e))</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr"/>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E39" t="inlineStr">
         <is>
           <t>-</t>
@@ -12548,7 +12542,11 @@
           <t>Lease liabilities (Note 7)</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr"/>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E43" t="inlineStr">
         <is>
           <t>-</t>
@@ -13154,7 +13152,11 @@
           <t>Lease liabilities (Notes 7 and 14)</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr"/>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E49" t="inlineStr">
         <is>
           <t>-</t>
@@ -24375,7 +24377,11 @@
           <t>Acquisition of intangible assets</t>
         </is>
       </c>
-      <c r="D164" t="inlineStr"/>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E164" t="inlineStr">
         <is>
           <t>-</t>
